--- a/checklist_forms/041_horror_movie_checklist--checklist_forms.xlsx
+++ b/checklist_forms/041_horror_movie_checklist--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rewatched</t>
+          <t>Watched Rewatched Rewatched</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Watched Time</t>
+          <t>Watched Watched Rewatched Time</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rewatched Language</t>
+          <t>Watched Rewatched Rewatched Language</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Rewatched Notes</t>
+          <t>Watched Rewatched Rewatched Notes</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1233,80 +1233,80 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>watched_rating_choices</t>
+          <t>watched_watched_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>watched_rating_choices</t>
+          <t>watched_watched_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>watched_watched_choices</t>
+          <t>watched_watched_language_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>watched_watched_choices</t>
+          <t>watched_watched_language_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>english</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1335,46 +1335,46 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>spanish</t>
+          <t>mandarin</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>Mandarin</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>watched_watched_language_choices</t>
+          <t>watched_rewatched_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>french</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>watched_watched_language_choices</t>
+          <t>watched_rewatched_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>mandarin</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mandarin</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1386,46 +1386,46 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Maybe</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>watched_rewatched_choices</t>
+          <t>watched_rewatched_language_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>watched_rewatched_choices</t>
+          <t>watched_rewatched_language_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>maybe</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>english</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1454,46 +1454,46 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>spanish</t>
+          <t>mandarin</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>Mandarin</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>watched_rewatched_language_choices</t>
+          <t>watched_recommendation_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>french</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>watched_rewatched_language_choices</t>
+          <t>watched_recommendation_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>mandarin</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mandarin</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1505,46 +1505,46 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Maybe</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>watched_recommendation_choices</t>
+          <t>watched_rewatched_rewatched_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>watched_recommendation_choices</t>
+          <t>watched_rewatched_rewatched_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>maybe</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1556,46 +1556,46 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Maybe</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>watched_rewatched_rewatched_choices</t>
+          <t>watched_rewatched_rewatched_language_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>watched_rewatched_rewatched_choices</t>
+          <t>watched_rewatched_rewatched_language_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>maybe</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>english</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1624,44 +1624,10 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>spanish</t>
+          <t>mandarin</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
-        <is>
-          <t>Spanish</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>watched_rewatched_rewatched_language_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>french</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>French</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>watched_rewatched_rewatched_language_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>mandarin</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
         <is>
           <t>Mandarin</t>
         </is>
